--- a/data/lab_data.xlsx
+++ b/data/lab_data.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R3b622aecf3364553"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News" sheetId="2" r:id="R3b83366dd3c548cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Activities" sheetId="3" r:id="Rb9404110bc604cc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publications" sheetId="4" r:id="R96c753846ebd4f1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="5" r:id="R1e22f71d94a44fbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alumni" sheetId="6" r:id="Rf3319ffc12a04544"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaborators" sheetId="7" r:id="R79f1435117a44bb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FacultyProfile" sheetId="8" r:id="R39a3167ea3294cf6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SiteSettings" sheetId="9" r:id="R191769b1c7dc4ec9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="10" r:id="R8da57c43122b4a89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tags" sheetId="11" r:id="Rb665e2c07c84458d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R00c97fbee51347cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News" sheetId="2" r:id="R38c665f38eec4723"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Activities" sheetId="3" r:id="R2f647d9536714ca0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publications" sheetId="4" r:id="R6ddc88cd6ab246ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="5" r:id="R618eb30d931d422b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alumni" sheetId="6" r:id="R1edfd92daf5e4cd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collaborators" sheetId="7" r:id="R6203f7440e564388"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FacultyProfile" sheetId="8" r:id="R9878d3cebe504210"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SiteSettings" sheetId="9" r:id="R37b07a9df8c24bd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="10" r:id="R90be88ab880c4c03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tags" sheetId="11" r:id="Raca45e9e53884524"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2021,7 +2021,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
-        <x:v>2026.10.01</x:v>
+        <x:v>2026.10.07</x:v>
       </x:c>
       <x:c r="B6" t="str">
         <x:v>COLLABORATION</x:v>
